--- a/data/trans_orig/IP04D$individual-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25452</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35447</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51261</t>
+          <t>51206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>64314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>86402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50352</t>
+          <t>50274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64481</t>
+          <t>65985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54316</t>
+          <t>53830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93117</t>
+          <t>93295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114622</t>
+          <t>115383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43740</t>
+          <t>44867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34780</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50733</t>
+          <t>50250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65459</t>
+          <t>67616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88052</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>47608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46045</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>62653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101202</t>
+          <t>99518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123795</t>
+          <t>121638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,27%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32539</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39847</t>
+          <t>41404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61723</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>53560</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66716</t>
+          <t>67317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54964</t>
+          <t>54285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>68331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111324</t>
+          <t>112527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>131643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44235</t>
+          <t>44956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64417</t>
+          <t>65828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55015</t>
+          <t>55317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78242</t>
+          <t>77102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104905</t>
+          <t>105419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136242</t>
+          <t>136110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141691</t>
+          <t>140280</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161873</t>
+          <t>161152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149236</t>
+          <t>150376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172463</t>
+          <t>172161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297343</t>
+          <t>297475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328680</t>
+          <t>328166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42822</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>31615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49140</t>
+          <t>49347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61156</t>
+          <t>61256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86669</t>
+          <t>86902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104732</t>
+          <t>105058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122650</t>
+          <t>121965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91263</t>
+          <t>91056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109218</t>
+          <t>108788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201289</t>
+          <t>201056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226802</t>
+          <t>226702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16581</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36682</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36636</t>
+          <t>35885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51214</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62378</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90574</t>
+          <t>90825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105874</t>
+          <t>106589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173752</t>
+          <t>173903</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212756</t>
+          <t>210373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>213764</t>
+          <t>215518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>255806</t>
+          <t>255938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>400285</t>
+          <t>395741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455411</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>462689</t>
+          <t>465072</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>501693</t>
+          <t>501542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>459545</t>
+          <t>459413</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>501587</t>
+          <t>499833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>935385</t>
+          <t>935357</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>990511</t>
+          <t>995055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>40780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28306</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43968</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58318</t>
+          <t>59967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79626</t>
+          <t>80922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>42310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56629</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55070</t>
+          <t>55668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70732</t>
+          <t>70851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102502</t>
+          <t>101206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123810</t>
+          <t>122161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46158</t>
+          <t>46165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37208</t>
+          <t>37753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>54078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72714</t>
+          <t>72830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96674</t>
+          <t>96083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58263</t>
+          <t>58256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74505</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>57998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74868</t>
+          <t>74323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119823</t>
+          <t>120414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143783</t>
+          <t>143667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35345</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46068</t>
+          <t>45682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40008</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53359</t>
+          <t>54121</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95423</t>
+          <t>96840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59747</t>
+          <t>58505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81837</t>
+          <t>81064</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44890</t>
+          <t>44826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65006</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110413</t>
+          <t>110620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141327</t>
+          <t>142750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141740</t>
+          <t>142513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163830</t>
+          <t>165072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143756</t>
+          <t>143757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163872</t>
+          <t>163936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291012</t>
+          <t>289589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321926</t>
+          <t>321719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19268</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>32733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>35496</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101081</t>
+          <t>102798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116263</t>
+          <t>117362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107378</t>
+          <t>106927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122948</t>
+          <t>122544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213247</t>
+          <t>215003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235138</t>
+          <t>236109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49525</t>
+          <t>48695</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46984</t>
+          <t>48029</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58737</t>
+          <t>58549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89349</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105638</t>
+          <t>105380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188911</t>
+          <t>188024</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225511</t>
+          <t>225213</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186066</t>
+          <t>183875</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>224581</t>
+          <t>225686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>382660</t>
+          <t>383674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>437949</t>
+          <t>441812</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>444035</t>
+          <t>444333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>480635</t>
+          <t>481522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>480323</t>
+          <t>479218</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>518838</t>
+          <t>521029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>936502</t>
+          <t>932639</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>991791</t>
+          <t>990777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32403</t>
+          <t>32532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>26808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50418</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75811</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72059</t>
+          <t>71930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86661</t>
+          <t>85996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88053</t>
+          <t>87839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106873</t>
+          <t>108450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163908</t>
+          <t>164295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189301</t>
+          <t>189358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32533</t>
+          <t>32550</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>54974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66296</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79787</t>
+          <t>79907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63040</t>
+          <t>63023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79032</t>
+          <t>79010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135361</t>
+          <t>135280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>155617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>19922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39971</t>
+          <t>41022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>49189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>50546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59756</t>
+          <t>59946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94817</t>
+          <t>95792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107322</t>
+          <t>107727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41471</t>
+          <t>40734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>34518</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60116</t>
+          <t>62391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58744</t>
+          <t>58062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94131</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176355</t>
+          <t>177092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198387</t>
+          <t>199715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158156</t>
+          <t>155881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183127</t>
+          <t>183754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341966</t>
+          <t>341231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377353</t>
+          <t>378035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>56806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76113</t>
+          <t>78106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98695</t>
+          <t>98828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>110425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106716</t>
+          <t>105811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145950</t>
+          <t>145649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205932</t>
+          <t>203939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252795</t>
+          <t>251975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50794</t>
+          <t>50716</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62584</t>
+          <t>61945</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54580</t>
+          <t>55909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66580</t>
+          <t>66723</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110449</t>
+          <t>110714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126749</t>
+          <t>127164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87890</t>
+          <t>89786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123198</t>
+          <t>123911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131688</t>
+          <t>130641</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189080</t>
+          <t>182493</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>228763</t>
+          <t>230995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295724</t>
+          <t>295545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>533955</t>
+          <t>533242</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>569263</t>
+          <t>567367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>558495</t>
+          <t>565082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>615887</t>
+          <t>616934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1109004</t>
+          <t>1109183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1175965</t>
+          <t>1173733</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$individual-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43633</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36466</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51542</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,62%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32100</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23948</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39659</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25384</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40383</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43633</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>35933</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51206</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>48,61%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64314</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>85695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46130</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38221</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53297</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57833</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50274</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65985</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49550</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>64549</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>64,31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46130</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38557</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>53830</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93295</t>
+          <t>94002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115383</t>
+          <t>115255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42319</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33683</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50443</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>43,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>35870</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28805</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44867</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>28406</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>43457</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>38,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>48,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>42319</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>34125</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>50250</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>43,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67616</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89736</t>
+          <t>89209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54459</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46335</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63095</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>56,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>56605</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47608</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63670</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>49018</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>64069</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>61,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>51,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>54459</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>46528</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>62653</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>56,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99518</t>
+          <t>100045</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121638</t>
+          <t>121528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25007</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18830</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33010</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25491</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18840</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32597</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19210</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33403</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25007</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>18559</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>32605</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41404</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>60941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -1526,67 +1526,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>61883</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53880</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68060</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>60666</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53560</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67317</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52754</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>66947</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61883</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54285</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>68331</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>71,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112527</t>
+          <t>112106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131643</t>
+          <t>131369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>66066</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55903</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>78993</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>54211</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>44956</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65828</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>44464</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>66554</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>66066</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>55317</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>77102</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105419</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>134573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161412</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148485</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171575</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>75,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>151897</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140280</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161152</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>139554</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>161644</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161412</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>150376</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>172161</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297475</t>
+          <t>299012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328166</t>
+          <t>329740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39979</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30620</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48524</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,47%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33379</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25589</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42496</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>25637</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>41894</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>39979</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31615</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>49347</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,47%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61256</t>
+          <t>61105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86902</t>
+          <t>85484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>100424</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>91879</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>109783</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>114175</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>105058</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121965</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>105660</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121917</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>77,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>100424</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>91056</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>108788</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,53%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201056</t>
+          <t>202474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226702</t>
+          <t>226853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17031</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11690</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>23646</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>11251</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6955</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17332</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>6826</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>17414</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>21,14%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13,07%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>17031</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>12020</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>23934</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>23,0%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36431</t>
+          <t>36965</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57007</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>50392</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>62348</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>84,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>41966</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>35885</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>46262</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>35803</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>46391</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>78,86%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>86,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57007</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>62018</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>77,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90825</t>
+          <t>90291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106589</t>
+          <t>105744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,107 +2780,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>234035</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>214532</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>255127</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>32,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>29,99%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>35,66%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>192302</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>173903</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>210373</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>174636</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>212153</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>28,47%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>234035</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>215518</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>255938</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>31,41%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>426337</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>398665</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>455051</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>30,65%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>28,66%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>32,72%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>35,78%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>426337</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>395741</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>455439</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>30,65%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -2893,107 +2893,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>481316</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>460224</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>500819</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>67,28%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>64,34%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>70,01%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>483143</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>465072</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>501542</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>463292</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>500809</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>71,53%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>74,25%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>481316</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>459413</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>499833</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>68,59%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>74,14%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>964459</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>935745</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>992131</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>69,35%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>67,28%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>64,22%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>69,87%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>964459</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>935357</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>995055</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>69,35%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>976</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,74 +3357,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35834</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28751</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44054</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33517</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26240</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40780</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26989</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40779</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>40,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>49,08%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35834</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28187</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>43370</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>28,46%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>43,79%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>105</t>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>58943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80922</t>
+          <t>80126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63204</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54984</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>70287</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>49573</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42310</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56850</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42311</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>56101</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>59,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>50,92%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63204</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55668</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70851</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101206</t>
+          <t>102002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122161</t>
+          <t>123185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38331</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>54874</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>37800</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30385</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46165</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30582</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>46505</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>36,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>46220</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>37753</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>54078</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,24%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72830</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96083</t>
+          <t>96080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65856</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>57202</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>73745</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>66621</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58256</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74036</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57916</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>73839</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>63,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>65856</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>57998</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>74323</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>58,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120414</t>
+          <t>120417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>144513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27900</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20339</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34854</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>21166</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16158</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27561</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15440</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27743</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27900</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20661</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>34740</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>39907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59167</t>
+          <t>57719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46882</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39928</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54443</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>40674</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34279</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45682</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>34097</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>46400</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>46882</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>40042</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>54121</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77455</t>
+          <t>78903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96840</t>
+          <t>96715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54019</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44316</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64788</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>70557</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>58505</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>81064</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>59733</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>81915</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54019</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44826</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>65005</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110620</t>
+          <t>111149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142750</t>
+          <t>139772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>154743</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143974</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>164446</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>153020</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>142513</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>165072</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>141662</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>163844</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>154743</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>143757</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>163936</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289589</t>
+          <t>292567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321719</t>
+          <t>321190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26708</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20025</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36626</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25732</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18169</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32733</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18659</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>33787</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,99%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>26708</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19879</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35496</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>42181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>115715</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>105797</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>122398</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>109799</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102798</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117362</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>101744</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>116872</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,01%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>86,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>115715</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>106927</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>122544</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215003</t>
+          <t>213572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236109</t>
+          <t>235773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13730</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9080</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19548</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>17178</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>12392</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23823</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>11698</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>23254</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>28,12%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20,29%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>13730</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>9276</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>19796</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39390</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>54095</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>48277</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>58745</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>79,76%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>71,18%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,61%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>43909</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>37264</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>48695</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>37833</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>49389</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>71,88%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>61,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>79,71%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>54095</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>48029</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>58549</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>79,76%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89522</t>
+          <t>89994</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105380</t>
+          <t>105301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>204410</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>184234</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>224780</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>205949</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>188024</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>225213</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>187930</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>226716</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>30,76%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>204410</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>183875</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>225686</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>383674</t>
+          <t>383325</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>441812</t>
+          <t>438725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>500494</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>480124</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>520670</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>68,11%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>73,86%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>694</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>463597</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>444333</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>481522</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>442830</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>481616</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>69,24%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>66,36%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>500494</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>479218</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>521029</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>932639</t>
+          <t>935726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>990777</t>
+          <t>991126</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -5646,52 +5646,52 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35511</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27965</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44941</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>24319</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18466</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32532</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37828</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47419</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>62146</t>
+          <t>59965</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75424</t>
+          <t>72574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80143</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71930</t>
+          <t>76060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85996</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97430</t>
+          <t>78473</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87839</t>
+          <t>70662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108450</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>177573</t>
+          <t>163963</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164295</t>
+          <t>151354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189358</t>
+          <t>175201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21605</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15280</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29245</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>20991</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14774</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28220</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32550</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>42078</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>32396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54974</t>
+          <t>53387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>69793</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>62153</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76118</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>73690</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>66461</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79907</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>77,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>72443</t>
+          <t>76073</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63023</t>
+          <t>69015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>82373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>146132</t>
+          <t>145866</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135280</t>
+          <t>134557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155617</t>
+          <t>155548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,76%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7126</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3599</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11802</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5819</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2672</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10839</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49815</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45139</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53342</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>46042</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41022</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49189</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56069</t>
+          <t>47661</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50546</t>
+          <t>42616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59946</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>102111</t>
+          <t>97476</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95792</t>
+          <t>90198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107727</t>
+          <t>102256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42252</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30113</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56191</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>29851</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18111</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40734</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45826</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34518</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>75678</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>56725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94866</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159692</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>145753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171831</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>187975</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>177092</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>199715</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86,3%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>172446</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155881</t>
+          <t>141124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183754</t>
+          <t>157241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>360419</t>
+          <t>309441</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341231</t>
+          <t>293571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>378035</t>
+          <t>323803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25931</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15989</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54568</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13899</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9003</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20600</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56806</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78106</t>
+          <t>69409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>122312</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>93675</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>132254</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>82,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>105529</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>98828</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>110425</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>88,36%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>133477</t>
+          <t>104930</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105811</t>
+          <t>97970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145649</t>
+          <t>109806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>239006</t>
+          <t>227242</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203939</t>
+          <t>197565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251975</t>
+          <t>238655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9239</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>16085</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>11541</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6950</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18179</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,39%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30184</t>
+          <t>31331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59048</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>52202</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>63434</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>57354</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>50716</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61945</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,61%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62089</t>
+          <t>57830</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55909</t>
+          <t>50395</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66723</t>
+          <t>63171</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>119443</t>
+          <t>116879</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110714</t>
+          <t>107313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127164</t>
+          <t>124128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>141665</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>121386</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>172083</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>106420</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>89786</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>123911</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>18,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>153623</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130641</t>
+          <t>89619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182493</t>
+          <t>122860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>260043</t>
+          <t>247574</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230995</t>
+          <t>221162</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295545</t>
+          <t>280805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>546149</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>515731</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>566428</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>74,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>777</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>550733</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>533242</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>567367</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>81,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>593952</t>
+          <t>514717</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>565082</t>
+          <t>497767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>531008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1144685</t>
+          <t>1060867</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1109183</t>
+          <t>1027636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1173733</t>
+          <t>1087279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
